--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>5.9</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>8.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>5.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.45</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.9</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>8.5</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1376,10 +1376,10 @@
         <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.9</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.33</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.33</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.33</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>5.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.31</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>2.39</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.33</v>
       </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.92</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.39</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,16 +1299,16 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,16 +1418,16 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
         <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.66</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>3.37</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH10" t="n">
         <v>3.25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V11" t="n">
         <v>5</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.26</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.37</v>
+        <v>2.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.06</v>
+        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="M12" t="n">
-        <v>5.25</v>
+        <v>3.66</v>
       </c>
       <c r="N12" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>3.26</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.14</v>
+        <v>3.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.47</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S13" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>4.31</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.31</v>
+        <v>3.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="N10" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>3.78</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.9</v>
+        <v>2.63</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.14</v>
+        <v>2.58</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH11" t="n">
         <v>3.25</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.26</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V7" t="n">
         <v>5</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>1.33</v>
       </c>
       <c r="O8" t="n">
-        <v>2.33</v>
+        <v>7.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.12</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.01</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>2.05</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.23</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.26</v>
+        <v>2.06</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.66</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.97</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.26</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.37</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>4.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.31</v>
+        <v>3.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>5.25</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.39</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>4.47</v>
+        <v>4.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.97</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V15" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
         <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>4.12</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>4.33</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>1.33</v>
       </c>
       <c r="O7" t="n">
-        <v>2.28</v>
+        <v>7.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="W7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.12</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2.01</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.27</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>5.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>2.92</v>
+        <v>3.84</v>
       </c>
       <c r="T10" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>7.6</v>
+        <v>4.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.37</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC11" t="n">
         <v>3.37</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AD11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.23</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>3.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.61</v>
+        <v>2.43</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -2276,125 +2276,6 @@
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>46035</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dunbeholden</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Molynes United</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>46035.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>1.33</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
-        <v>7.26</v>
+        <v>2.28</v>
       </c>
       <c r="P7" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>2.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>3.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.61</v>
+        <v>2.43</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.43</v>
+        <v>5.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="W12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.11</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.36</v>
+        <v>3.25</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="AC13" t="n">
         <v>2.74</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>4.88</v>
+        <v>4.47</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7.26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.27</v>
+        <v>2.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>5.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>2.92</v>
+        <v>3.84</v>
       </c>
       <c r="T11" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>7.6</v>
+        <v>4.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>2.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.37</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="P12" t="n">
-        <v>2.64</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.61</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.84</v>
+        <v>2.92</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.33</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.64</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>3.37</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>4.88</v>
+        <v>4.47</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.11</v>
+        <v>2.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.18</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="AC15" t="n">
         <v>2.74</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>4.31</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.28</v>
+        <v>7.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>4.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.01</v>
+        <v>1.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC10" t="n">
         <v>3.37</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.36</v>
+        <v>2.23</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.64</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>2.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>3.82</v>
       </c>
       <c r="P11" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.61</v>
+        <v>2.57</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.84</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.25</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.06</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1995,10 +1995,10 @@
         <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.08</v>
@@ -2007,10 +2007,10 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>3.43</v>
       </c>
       <c r="AA13" t="n">
         <v>2</v>
@@ -2019,7 +2019,7 @@
         <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD13" t="n">
         <v>1.31</v>
@@ -2028,13 +2028,13 @@
         <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2105,13 +2105,13 @@
         <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
         <v>2.47</v>
       </c>
       <c r="T14" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="U14" t="n">
         <v>1.25</v>
@@ -2141,7 +2141,7 @@
         <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
         <v>1.98</v>
@@ -2150,7 +2150,7 @@
         <v>1.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
         <v>1.53</v>
@@ -2215,13 +2215,13 @@
         <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="R15" t="n">
         <v>1.28</v>
@@ -2233,13 +2233,13 @@
         <v>2.54</v>
       </c>
       <c r="U15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
         <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
@@ -2263,16 +2263,16 @@
         <v>1.42</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AG15" t="n">
         <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.36</v>
+        <v>3.82</v>
       </c>
       <c r="P10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.7</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.45</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.37</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.23</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.82</v>
+        <v>2.36</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>5.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.97</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z11" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>4.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>4.47</v>
+        <v>4.93</v>
       </c>
       <c r="P13" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U13" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
         <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.43</v>
+        <v>3.98</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.04</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>2.96</v>
+        <v>4.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>2.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.25</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.74</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.94</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.41</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.19</v>
+        <v>4.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.54</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.12</v>
+        <v>2.61</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.31</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
         <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>4.31</v>
       </c>
       <c r="O7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.64</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.82</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>6.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>3.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="M12" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V12" t="n">
         <v>5.1</v>
       </c>
-      <c r="N12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.33</v>
-      </c>
       <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.16</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z12" t="n">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
-        <v>4.93</v>
+        <v>4.42</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.18</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
         <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.98</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.6</v>
+        <v>4.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>4.42</v>
+        <v>4.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
         <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N7" t="n">
-        <v>4.31</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>4.31</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.61</v>
-      </c>
-      <c r="V8" t="n">
-        <v>5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
         <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V10" t="n">
         <v>5.1</v>
       </c>
-      <c r="N10" t="n">
-        <v>7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.33</v>
-      </c>
       <c r="W10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.16</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.27</v>
+        <v>2.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.97</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>7.6</v>
+        <v>4.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.02</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.37</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.23</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.35</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.82</v>
+        <v>2.36</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.57</v>
+        <v>5.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.32</v>
+        <v>2.23</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.32</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>4.93</v>
+        <v>2.97</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>4.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.53</v>
+        <v>3.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.98</v>
+        <v>2.61</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>4.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>4.32</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>4.93</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>3.18</v>
       </c>
       <c r="T15" t="n">
-        <v>3.38</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.61</v>
+        <v>3.98</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>4.31</v>
       </c>
       <c r="O7" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.61</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.31</v>
+        <v>3.85</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
         <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.64</v>
+        <v>5.1</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.82</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>6.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>4.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>3.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V11" t="n">
         <v>5.1</v>
       </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.33</v>
-      </c>
       <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.16</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z11" t="n">
-        <v>5.55</v>
+        <v>4.45</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.2</v>
+        <v>4.32</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>2.97</v>
+        <v>4.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.25</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
-        <v>3.38</v>
+        <v>2.53</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.61</v>
+        <v>3.98</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.32</v>
+        <v>2.2</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.93</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>4.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>3.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.98</v>
+        <v>2.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.11</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>4.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.51736111111</v>
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="N6" t="n">
         <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
         <v>5.35</v>
@@ -1171,31 +1171,31 @@
         <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
         <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
         <v>1.11</v>
@@ -1254,49 +1254,49 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>4.31</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
         <v>1.61</v>
@@ -1305,22 +1305,22 @@
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>3.85</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
         <v>1.61</v>
@@ -1406,28 +1406,28 @@
         <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
         <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
         <v>1.54</v>
@@ -1439,7 +1439,7 @@
         <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.1</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>3.84</v>
       </c>
       <c r="P10" t="n">
-        <v>2.77</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.9</v>
+        <v>2.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>4.33</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.64</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.08</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.82</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.57</v>
+        <v>6.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>6.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>2.97</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
         <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.97</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
         <v>7.6</v>
@@ -1891,31 +1891,31 @@
         <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.37</v>
+        <v>3.29</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.27</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH12" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.42</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.49</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.08</v>
+        <v>4.55</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2087,37 +2087,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.32</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.93</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.11</v>
@@ -2129,31 +2129,31 @@
         <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
         <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T15" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.55</v>
+        <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.61</v>
+        <v>6.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>5.65</v>
+        <v>7.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>3.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>3.84</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.2</v>
+        <v>2.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.97</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
         <v>1.7</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.41</v>
       </c>
-      <c r="V12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.29</v>
+        <v>2.03</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>2.11</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.11</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.33</v>
       </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.949999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5.14</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>2.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>4.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC6" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>2.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>5.14</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>1.3</v>
       </c>
       <c r="O8" t="n">
-        <v>2.28</v>
+        <v>6.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.46</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.01</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U10" t="n">
         <v>1.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.41</v>
       </c>
-      <c r="V10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.29</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.61</v>
+        <v>6.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>5.65</v>
+        <v>7.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>3.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>3.84</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.2</v>
+        <v>2.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.97</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.11</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.33</v>
       </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.11</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>5.14</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>1.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.46</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.01</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8.949999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>5.14</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>1.3</v>
+        <v>3.91</v>
       </c>
       <c r="O8" t="n">
-        <v>6.5</v>
+        <v>2.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>4.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>2.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>3.84</v>
       </c>
       <c r="P10" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.2</v>
+        <v>2.61</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.97</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>1.41</v>
       </c>
-      <c r="V11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.29</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>2.97</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.61</v>
+        <v>6.05</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>5.65</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.49</v>
+        <v>3.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1980,7 +1980,7 @@
         <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
         <v>3.75</v>
@@ -1989,13 +1989,13 @@
         <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
         <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
         <v>9.4</v>
@@ -2019,22 +2019,22 @@
         <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.55</v>
+        <v>4.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2096,25 +2096,25 @@
         <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4.3</v>
+        <v>4.93</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="T14" t="n">
         <v>2.38</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V14" t="n">
         <v>5.5</v>
@@ -2126,10 +2126,10 @@
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>4.14</v>
       </c>
       <c r="AA14" t="n">
         <v>1.72</v>
@@ -2141,19 +2141,19 @@
         <v>2.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2269,7 +2269,7 @@
         <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.23</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="n">
         <v>1.25</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>3.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V5" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
         <v>1.27</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.51736111111</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.949999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5.14</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>2.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
@@ -1177,31 +1177,31 @@
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.65</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>7.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>5.14</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>7.6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.46</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB7" t="n">
         <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.46</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
         <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1611,25 +1611,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
         <v>3.36</v>
@@ -1641,7 +1641,7 @@
         <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>5.65</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
         <v>1.11</v>
@@ -1656,7 +1656,7 @@
         <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
         <v>2.3</v>
@@ -1665,7 +1665,7 @@
         <v>2.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="n">
         <v>1.53</v>
@@ -1674,7 +1674,7 @@
         <v>2.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="n">
         <v>1.35</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.75</v>
@@ -1745,7 +1745,7 @@
         <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.23</v>
@@ -1754,16 +1754,16 @@
         <v>3.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
         <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
@@ -1772,16 +1772,16 @@
         <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
         <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
         <v>1.78</v>
@@ -1790,13 +1790,13 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
         <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1852,22 +1852,22 @@
         <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
         <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="P12" t="n">
         <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
         <v>2.81</v>
@@ -1891,16 +1891,16 @@
         <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.28</v>
@@ -1909,10 +1909,10 @@
         <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
         <v>2.31</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.25</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.73</v>
+        <v>3.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O14" t="n">
-        <v>4.93</v>
+        <v>2.9</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.56</v>
+        <v>4.73</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
         <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
         <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
         <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P8" t="n">
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.88</v>
+        <v>2.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>2.81</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>3.54</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.93</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>2.31</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>3.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.9</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>2.81</v>
+        <v>3.94</v>
       </c>
       <c r="T12" t="n">
-        <v>2.89</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.41</v>
       </c>
-      <c r="V12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.31</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
         <v>3.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>4</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.28</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>2.16</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.49</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>1.88</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
         <v>1.25</v>
       </c>
-      <c r="V14" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.73</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.4</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.93</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.14</v>
+        <v>2.56</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>4.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.06</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
         <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
         <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
         <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
         <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.88</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>6.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>3.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>3.88</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.9</v>
+        <v>2.59</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="U12" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.61</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="O13" t="n">
-        <v>4.93</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>4.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>4.61</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>4.93</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U15" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="V15" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="Z15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.56</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.73</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
         <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
         <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
         <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF6" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.75</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.14</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>7.6</v>
+        <v>2.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.37</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>7.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>5.14</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
         <v>1.25</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
         <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>3.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.66</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>2.07</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>3.88</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.9</v>
+        <v>2.59</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.88</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.59</v>
+        <v>6.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="T12" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V12" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.35</v>
+        <v>3.24</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>4.61</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3.94</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>1.59</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>4.93</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.47</v>
+        <v>1.21</v>
       </c>
       <c r="Z13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.56</v>
       </c>
-      <c r="AA13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.73</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.61</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.59</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.93</v>
+        <v>2.9</v>
       </c>
       <c r="P15" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="T15" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="V15" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.56</v>
+        <v>4.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>7.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>5.14</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>1.28</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
         <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="M7" t="n">
         <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
         <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
         <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
         <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.06</v>
+        <v>1.82</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7.75</v>
+        <v>1.8</v>
       </c>
       <c r="M8" t="n">
-        <v>5.14</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
-        <v>7.6</v>
+        <v>2.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.37</v>
+        <v>4.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.07</v>
       </c>
       <c r="O10" t="n">
-        <v>2.21</v>
+        <v>3.88</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>2.81</v>
+        <v>3.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.89</v>
+        <v>2.42</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="V10" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.54</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>3.66</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.07</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.88</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>6.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.36</v>
+        <v>3.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>2.81</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.89</v>
       </c>
       <c r="U12" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="V12" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>3.54</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>2.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.24</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
         <v>1.37</v>
@@ -1040,7 +1040,7 @@
         <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
         <v>1.36</v>
@@ -1052,13 +1052,13 @@
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
         <v>1.24</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
         <v>1.93</v>
@@ -1067,22 +1067,22 @@
         <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
         <v>1.67</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.51736111111</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.75</v>
+        <v>1.78</v>
       </c>
       <c r="M6" t="n">
-        <v>5.14</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.28</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>3.61</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
         <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.37</v>
+        <v>4.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
         <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="O7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="T7" t="n">
         <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
         <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>5.15</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>1.32</v>
       </c>
       <c r="O8" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>2.07</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.88</v>
+        <v>2.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>5.95</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>3.36</v>
+        <v>2.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="U10" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V10" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>3.37</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.9</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.46</v>
       </c>
       <c r="U11" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>4.4</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.64</v>
+        <v>2.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q12" t="n">
-        <v>6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.89</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.61</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.94</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.93</v>
+        <v>2.98</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.16</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.56</v>
+        <v>4.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.49</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.88</v>
       </c>
       <c r="P14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.3</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.73</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,7 +618,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46035.38541666666</v>
+        <v>46035.41666666666</v>
       </c>
     </row>
     <row r="3">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,76 +897,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46035.41666666666</v>
+        <v>46035.51736111111</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.81</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>5.15</v>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>3.14</v>
+        <v>7.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.32</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46035.51736111111</v>
+        <v>46035.60416666666</v>
       </c>
     </row>
     <row r="6">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="T6" t="n">
         <v>2.36</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="V6" t="n">
         <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="R7" t="n">
         <v>1.29</v>
       </c>
       <c r="S7" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
         <v>2.36</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V7" t="n">
         <v>5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46035.60416666666</v>
+        <v>46035.625</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46035.625</v>
+        <v>46035.6875</v>
       </c>
     </row>
     <row r="10">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.95</v>
+        <v>6.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>2.85</v>
+        <v>3.94</v>
       </c>
       <c r="T10" t="n">
-        <v>2.96</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.41</v>
       </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.38</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.8</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.9</v>
+        <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>5.95</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>7.3</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>2.98</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.9</v>
+        <v>4.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>3.94</v>
+        <v>2.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.15</v>
+        <v>3.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>4.65</v>
+        <v>9.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.78</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.03</v>
+        <v>4.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.78</v>
+        <v>1.17</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.89</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46035.6875</v>
+        <v>46035.69791666666</v>
       </c>
     </row>
     <row r="13">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.25</v>
       </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.73</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2156,125 +2156,6 @@
         <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46035.69791666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>46035</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Northern Ireland NIFL Premiership</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Ballymena United</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Cliftonville</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI15" s="3" t="n">
         <v>46035.69791666666</v>
       </c>
     </row>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5.15</v>
+        <v>3.86</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>3.91</v>
       </c>
       <c r="O5" t="n">
-        <v>7.6</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.6</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.78</v>
+        <v>2.35</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>5.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.4</v>
+        <v>1.77</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.44</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.54</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.35</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>6.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>5.75</v>
+        <v>4.65</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>2.03</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.34</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.9</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="V10" t="n">
-        <v>4.65</v>
+        <v>5.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>2.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.89</v>
+        <v>1.34</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
       </c>
-      <c r="O13" t="n">
-        <v>4</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="AC13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.88</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.28</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,16 +823,16 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -1034,31 +1034,31 @@
         <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
         <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
         <v>1.6</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1501,31 +1501,31 @@
         <v>7.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
         <v>6.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V9" t="n">
-        <v>4.65</v>
+        <v>4.55</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1534,7 +1534,7 @@
         <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1.41</v>
@@ -1549,16 +1549,16 @@
         <v>1.78</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1623,28 +1623,28 @@
         <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
         <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1653,7 +1653,7 @@
         <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA10" t="n">
         <v>1.6</v>
@@ -1668,13 +1668,13 @@
         <v>1.45</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
         <v>1.34</v>
@@ -1742,10 +1742,10 @@
         <v>2.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.42</v>
@@ -1754,10 +1754,10 @@
         <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
@@ -1766,13 +1766,13 @@
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
         <v>1.95</v>
@@ -1781,22 +1781,22 @@
         <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD11" t="n">
         <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1858,7 +1858,7 @@
         <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="P12" t="n">
         <v>1.89</v>
@@ -1900,13 +1900,13 @@
         <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AF12" t="n">
         <v>1.72</v>
@@ -2028,7 +2028,7 @@
         <v>1.67</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AG13" t="n">
         <v>1.17</v>
@@ -2096,13 +2096,13 @@
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.42</v>
       </c>
       <c r="P14" t="n">
         <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
@@ -2111,13 +2111,13 @@
         <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U14" t="n">
         <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W14" t="n">
         <v>1.1</v>
@@ -2138,7 +2138,7 @@
         <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD14" t="n">
         <v>1.28</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -1019,19 +1019,19 @@
         <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4</v>
+        <v>4.56</v>
       </c>
       <c r="R5" t="n">
         <v>1.27</v>
@@ -1040,13 +1040,13 @@
         <v>3.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
         <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
         <v>1.12</v>
@@ -1055,22 +1055,22 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
         <v>1.54</v>
@@ -1079,7 +1079,7 @@
         <v>2.35</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
         <v>2.06</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="N8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
         <v>4.7</v>
       </c>
-      <c r="N8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.625</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>7.3</v>
+        <v>5.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.65</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.22</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>5.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.45</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.34</v>
+        <v>3.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.23</v>
+        <v>3.7</v>
       </c>
       <c r="P11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.36</v>
       </c>
-      <c r="Q11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.97</v>
+        <v>4.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.25</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.25</v>
       </c>
-      <c r="V12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z12" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4.88</v>
+        <v>2.97</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>4.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>3.18</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.98</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.06</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="N3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q3" t="n">
         <v>6.4</v>
       </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -903,25 +903,25 @@
         <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="U4" t="n">
         <v>1.36</v>
@@ -930,40 +930,40 @@
         <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.34</v>
+        <v>3.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
         <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
         <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46035.51736111111</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="M6" t="n">
-        <v>5.15</v>
+        <v>5.32</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>7.6</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.3</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V7" t="n">
         <v>5</v>
@@ -1290,37 +1290,37 @@
         <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC7" t="n">
         <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>4.42</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
         <v>2.49</v>
@@ -1873,40 +1873,40 @@
         <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
         <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="AD12" t="n">
         <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AF12" t="n">
         <v>1.96</v>
@@ -1968,34 +1968,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>3.23</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
         <v>9.4</v>
@@ -2007,34 +2007,34 @@
         <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4.88</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.38</v>
+        <v>2.76</v>
       </c>
       <c r="U14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.98</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.78</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>1.83</v>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.67</v>
+        <v>6.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>2.79</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.4</v>
+        <v>2.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.79</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>8.06</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>5.32</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>1.27</v>
       </c>
       <c r="O5" t="n">
-        <v>2.31</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.54</v>
+        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.06</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5.32</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.27</v>
       </c>
-      <c r="O6" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>2.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>6.08</v>
+        <v>5.25</v>
       </c>
       <c r="N8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P8" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
         <v>2.27</v>
@@ -1415,31 +1415,31 @@
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
         <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.625</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="N9" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.17</v>
+        <v>2.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N10" t="n">
         <v>5.25</v>
       </c>
-      <c r="N10" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.97</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.24</v>
+        <v>2.3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.8</v>
+        <v>2.14</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="N12" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q12" t="n">
         <v>4</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.49</v>
-      </c>
       <c r="R12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.36</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.14</v>
+        <v>4.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3.16</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AD13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
       <c r="M2" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>6.7</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="P2" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.4</v>
+        <v>2.67</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="U2" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.79</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>1.83</v>
       </c>
       <c r="P3" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.67</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>2.79</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8.06</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5.32</v>
+        <v>3.95</v>
       </c>
       <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.27</v>
       </c>
-      <c r="O5" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF5" t="n">
         <v>2.35</v>
       </c>
-      <c r="AC5" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.07</v>
+        <v>2.06</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="O6" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.25</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>8.06</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>5.32</v>
       </c>
       <c r="N7" t="n">
-        <v>3.83</v>
+        <v>1.27</v>
       </c>
       <c r="O7" t="n">
-        <v>2.28</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>3.4</v>
       </c>
       <c r="M9" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.5</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="U9" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.17</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.24</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="N10" t="n">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.17</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>5.25</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.59</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.25</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.78</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="O2" t="n">
-        <v>3.44</v>
+        <v>1.82</v>
       </c>
       <c r="P2" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.67</v>
+        <v>6.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.23</v>
+        <v>2.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>2.63</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83</v>
+        <v>3.44</v>
       </c>
       <c r="P3" t="n">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.4</v>
+        <v>2.67</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="V3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="W3" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.79</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.75</v>
+        <v>8.06</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>5.32</v>
       </c>
       <c r="N6" t="n">
-        <v>3.83</v>
+        <v>1.27</v>
       </c>
       <c r="O6" t="n">
-        <v>2.28</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.9</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.06</v>
+        <v>1.75</v>
       </c>
       <c r="M7" t="n">
-        <v>5.32</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.27</v>
+        <v>3.83</v>
       </c>
       <c r="O7" t="n">
-        <v>8.050000000000001</v>
+        <v>2.28</v>
       </c>
       <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.56</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.07</v>
+        <v>1.9</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M8" t="n">
         <v>5.25</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="P8" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.9</v>
+        <v>3.68</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.625</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="O13" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.7</v>
+        <v>3.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.49</v>
+        <v>2.22</v>
       </c>
       <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.36</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="N2" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.82</v>
+        <v>3.45</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.4</v>
+        <v>2.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="T2" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="V2" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.63</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="O3" t="n">
-        <v>3.44</v>
+        <v>1.85</v>
       </c>
       <c r="P3" t="n">
-        <v>2.27</v>
+        <v>2.54</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.67</v>
+        <v>6.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="W3" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2.25</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>2.76</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.37</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.49</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AD4" t="n">
         <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46035.51736111111</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>10.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>1.22</v>
       </c>
       <c r="O5" t="n">
-        <v>2.31</v>
+        <v>8.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.56</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.99</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.43</v>
+        <v>2.27</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.35</v>
+        <v>1.74</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.06</v>
+        <v>1.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.06</v>
+        <v>1.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5.32</v>
+        <v>3.86</v>
       </c>
       <c r="N6" t="n">
-        <v>1.27</v>
+        <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>8.050000000000001</v>
+        <v>2.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.2</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.76</v>
+        <v>2.37</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>2.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1254,31 +1254,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U7" t="n">
         <v>1.5</v>
@@ -1299,28 +1299,28 @@
         <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.68</v>
@@ -1418,16 +1418,16 @@
         <v>4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
         <v>2.31</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="N9" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
         <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
         <v>2.59</v>
@@ -1513,10 +1513,10 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
         <v>1.53</v>
@@ -1534,13 +1534,13 @@
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
         <v>2.62</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.25</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.29</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.24</v>
+        <v>2.18</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>4.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.65</v>
+        <v>5.65</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.97</v>
+        <v>2.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.17</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>3.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.14</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.16</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.45</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.23</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.49</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>3.38</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.16</v>
+        <v>4.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
         <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.05</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
-        <v>8.75</v>
+        <v>2.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
         <v>1.19</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z5" t="n">
-        <v>4.99</v>
+        <v>4.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.55</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.02</v>
+        <v>1.91</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>10.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.27</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.91</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.5</v>
+        <v>6.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="T8" t="n">
         <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
         <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.31</v>
+        <v>2.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.625</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>2.29</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>5.4</v>
       </c>
       <c r="R9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.25</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>2.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O10" t="n">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.4</v>
+        <v>2.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.15</v>
+        <v>2.49</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.77</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
       <c r="AC12" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.85</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>2.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.36</v>
+        <v>3.08</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>6.2</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.77</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AF14" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC14" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>10.7</v>
       </c>
       <c r="M5" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>1.22</v>
       </c>
       <c r="O5" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.27</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.52</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>3.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.91</v>
+        <v>1.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10.7</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.22</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>8.75</v>
+        <v>2.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.19</v>
       </c>
-      <c r="S7" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z7" t="n">
-        <v>4.99</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.27</v>
+        <v>2.52</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.55</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>1.91</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>3.37</v>
       </c>
       <c r="M9" t="n">
-        <v>3.56</v>
+        <v>3.61</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>2.29</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.4</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.81</v>
+        <v>2.46</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.18</v>
+        <v>1.35</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.37</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.01</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.59</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
-        <v>5.2</v>
+        <v>4.25</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.62</v>
+        <v>2.03</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>3.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>2.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>4.25</v>
+        <v>7.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.65</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>3.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.24</v>
+        <v>2.18</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -662,37 +662,37 @@
         <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="O2" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="U2" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1.02</v>
@@ -704,28 +704,28 @@
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AD2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE2" t="n">
         <v>1.48</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AF2" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AG2" t="n">
         <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="N3" t="n">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="P3" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.07</v>
+        <v>6.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
         <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.76</v>
+        <v>2.53</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -1144,40 +1144,40 @@
         <v>3.91</v>
       </c>
       <c r="O6" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="AA6" t="n">
         <v>1.6</v>
@@ -1192,16 +1192,16 @@
         <v>1.63</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.37</v>
+        <v>2.71</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.65</v>
@@ -1418,13 +1418,13 @@
         <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1.52</v>
@@ -1501,64 +1501,64 @@
         <v>2.01</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="T9" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="V9" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.22</v>
       </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH10" t="n">
-        <v>3.24</v>
+        <v>2.12</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.79</v>
+        <v>2.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.17</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.49</v>
+        <v>2.29</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>2.91</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2</v>
       </c>
-      <c r="AB12" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC12" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O13" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4.75</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.54</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N14" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.85</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>3.38</v>
+        <v>2.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.75</v>
+        <v>3.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -893,77 +893,77 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.8</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA4" t="n">
         <v>2.07</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AB4" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46035.51736111111</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>1.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6</v>
+        <v>3.86</v>
       </c>
       <c r="N5" t="n">
-        <v>1.22</v>
+        <v>3.91</v>
       </c>
       <c r="O5" t="n">
-        <v>8.75</v>
+        <v>2.22</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S5" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="T5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.2</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.74</v>
+        <v>2.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.8</v>
+        <v>9.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3.86</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>3.91</v>
+        <v>1.26</v>
       </c>
       <c r="O6" t="n">
-        <v>2.22</v>
+        <v>8.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>1.62</v>
       </c>
       <c r="R6" t="n">
         <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="T6" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>4.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.15</v>
+        <v>5.64</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.71</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>4.05</v>
       </c>
       <c r="AA7" t="n">
         <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.31</v>
+        <v>2.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.52</v>
+        <v>2.73</v>
       </c>
       <c r="AD7" t="n">
         <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1373,40 +1373,40 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="N8" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="O8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.65</v>
       </c>
-      <c r="P8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.61</v>
-      </c>
       <c r="V8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
@@ -1418,28 +1418,28 @@
         <v>4.75</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46035.625</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.37</v>
+        <v>1.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>2.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.61</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="U9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V9" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.34</v>
+        <v>2.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.56</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="T10" t="n">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>3.37</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>7.3</v>
+        <v>2.01</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>2.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.53</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.41</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.34</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.85</v>
+        <v>2.95</v>
       </c>
       <c r="N12" t="n">
-        <v>1.55</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.29</v>
+        <v>3.78</v>
       </c>
       <c r="R12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.33</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>2.95</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>3.38</v>
+        <v>2.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.75</v>
+        <v>3.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.95</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.36</v>
+        <v>2.83</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,25 +633,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="N2" t="n">
-        <v>2.07</v>
+        <v>6.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>1.78</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.6</v>
+        <v>6.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.39</v>
+        <v>1.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>2.53</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,99 +752,99 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V3" t="n">
         <v>4.9</v>
       </c>
-      <c r="N3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.5</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.53</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="M5" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="P5" t="n">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.7</v>
+        <v>4.62</v>
       </c>
       <c r="R5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.21</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH5" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9.75</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.26</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>8.4</v>
+        <v>2.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.62</v>
+        <v>3.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.64</v>
+        <v>6.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.02</v>
+        <v>2.19</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.76</v>
+        <v>9.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.32</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="O9" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="P9" t="n">
         <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>3.12</v>
       </c>
       <c r="T9" t="n">
         <v>2.57</v>
       </c>
       <c r="U9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
-        <v>6.25</v>
+        <v>6.3</v>
       </c>
       <c r="W9" t="n">
         <v>1.09</v>
@@ -1534,31 +1534,31 @@
         <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AD9" t="n">
         <v>1.44</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH9" t="n">
         <v>2.08</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>2.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1611,67 +1611,67 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="R10" t="n">
         <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
         <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AG10" t="n">
         <v>1.2</v>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="N11" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
         <v>2.61</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="U11" t="n">
         <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
         <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AG11" t="n">
         <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1849,34 +1849,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="M12" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="O12" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.78</v>
+        <v>3.89</v>
       </c>
       <c r="R12" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="T12" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="U12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V12" t="n">
         <v>9.4</v>
@@ -1885,16 +1885,16 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
         <v>1.5</v>
@@ -1909,13 +1909,13 @@
         <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46035.69791666666</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.4</v>
+        <v>3.74</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>2.61</v>
       </c>
       <c r="R13" t="n">
         <v>1.38</v>
@@ -1998,28 +1998,28 @@
         <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
         <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
         <v>1.27</v>
@@ -2087,67 +2087,67 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.4</v>
+        <v>4.45</v>
       </c>
       <c r="M14" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
         <v>2.29</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
         <v>2.91</v>
       </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
         <v>6.3</v>
       </c>
       <c r="W14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.65</v>
+        <v>3.76</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
         <v>1.68</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AG14" t="n">
         <v>1.21</v>

--- a/jogos_2026-01-13.xlsx
+++ b/jogos_2026-01-13.xlsx
@@ -633,99 +633,99 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V2" t="n">
         <v>4.9</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.53</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46035.41666666666</v>
@@ -752,25 +752,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" t="n">
-        <v>3</v>
-      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="N3" t="n">
-        <v>2.07</v>
+        <v>6.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>1.78</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>6.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27</v>
+        <v>2.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.5</v>
+        <v>6.15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.39</v>
+        <v>1.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>2.53</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46035.41666666666</v>
@@ -990,16 +990,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -1008,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.76</v>
+        <v>9.75</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.32</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="P6" t="n">
-        <v>2.52</v>
+        <v>2.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.86</v>
+        <v>4.62</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1.16</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z6" t="n">
-        <v>6.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.59</v>
+        <v>2.16</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.77</v>
+        <v>1.45</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.56</v>
+        <v>2.19</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,22 +1228,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>9.75</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>8.4</v>
+        <v>2.21</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.62</v>
+        <v>3.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="U7" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.64</v>
+        <v>6.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>2.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>2.19</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46035.60416666666</v>
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.95</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="P9" t="n">
-        <v>2.21</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S9" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>2.57</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V9" t="n">
-        <v>6.3</v>
+        <v>4.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46035.6875</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1607,77 +1607,77 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>3.56</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>2.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.86</v>
+        <v>4.05</v>
       </c>
       <c r="P10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.58</v>
       </c>
-      <c r="Q10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>3.95</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>2.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.07</v>
+        <v>2.22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46035.6875</v>
@@ -1704,99 +1704,99 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.25</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>4.05</v>
+        <v>2.33</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.61</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
         <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46035.6875</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1964,77 +1964,77 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.74</v>
+        <v>4.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.73</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.61</v>
+        <v>2.29</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V13" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="AA13" t="n">
         <v>1.86</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46035.69791666666</v>
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>4.73</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.29</v>
+        <v>2.61</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46035.69791666666</v>
